--- a/public/student-accounts-template.xlsx
+++ b/public/student-accounts-template.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$H$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +50,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,10 +424,10 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -429,42 +435,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Student ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Group ID</t>
         </is>
@@ -487,7 +493,11 @@
           <t>Student@2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01000000000</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>general</t>
@@ -498,10 +508,103 @@
           <t>Secondary 1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Excel Import Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Use the exact columns and formats shown in the Students sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>general or azhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>General Groups</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1=Preparatory 1, 2=Preparatory 2, 3=Preparatory 3, 4=Secondary 1, 5=Secondary 2, 6=Secondary 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Azhar Groups</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1A=Preparatory 1, 2A=Preparatory 2, 3A=Preparatory 3, 4A=Secondary 1, 5A=Secondary 2, 6A=Secondary 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Preparatory 1 / Preparatory 2 / Preparatory 3 / Secondary 1 / Secondary 2 / Secondary 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Minimum 8 characters</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>